--- a/APS-Modules/aps-cx/src/main/resources/excelModel/CxDetail.xlsx
+++ b/APS-Modules/aps-cx/src/main/resources/excelModel/CxDetail.xlsx
@@ -1643,9 +1643,9 @@
         <v>43</v>
       </c>
       <c r="AG3" s="28"/>
-      <c r="AH3" s="27" t="e">
-        <f>SUM(N3+U3+AB3)</f>
-        <v>#VALUE!</v>
+      <c r="AH3" s="27">
+        <f>SUM(N3,U3,AB3)</f>
+        <v>0</v>
       </c>
       <c r="AI3" s="29"/>
       <c r="AJ3" s="30"/>
